--- a/experimentos/resultados/exp_cortes_fijos_v2_sin_prefiltro.xlsx
+++ b/experimentos/resultados/exp_cortes_fijos_v2_sin_prefiltro.xlsx
@@ -573,7 +573,7 @@
         <v>11</v>
       </c>
       <c r="H2">
-        <v>0.3306864408120098</v>
+        <v>0.3330977584985574</v>
       </c>
       <c r="I2">
         <v>243</v>
@@ -608,7 +608,7 @@
         <v>12</v>
       </c>
       <c r="H3">
-        <v>0.3334250328552366</v>
+        <v>0.3338869470669321</v>
       </c>
       <c r="I3">
         <v>494</v>
@@ -678,7 +678,7 @@
         <v>14</v>
       </c>
       <c r="H5">
-        <v>0.2893907313434707</v>
+        <v>0.2895860838080908</v>
       </c>
       <c r="I5">
         <v>1114</v>
@@ -713,13 +713,13 @@
         <v>15</v>
       </c>
       <c r="H6">
-        <v>0.3027932365704152</v>
+        <v>0.3041481724246964</v>
       </c>
       <c r="I6">
         <v>267</v>
       </c>
       <c r="J6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
         <v>44</v>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="H7">
-        <v>0.3121003052508522</v>
+        <v>0.3112469006501729</v>
       </c>
       <c r="I7">
         <v>380</v>
@@ -783,7 +783,7 @@
         <v>17</v>
       </c>
       <c r="H8">
-        <v>0.2324904620300301</v>
+        <v>0.2318200572860842</v>
       </c>
       <c r="I8">
         <v>300</v>
@@ -818,7 +818,7 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>0.4045803841727098</v>
+        <v>0.4056859857877074</v>
       </c>
       <c r="I9">
         <v>234</v>
@@ -888,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="H11">
-        <v>0.3985121931116696</v>
+        <v>0.3987859719456777</v>
       </c>
       <c r="I11">
         <v>598</v>
@@ -923,7 +923,7 @@
         <v>21</v>
       </c>
       <c r="H12">
-        <v>0.343994874687333</v>
+        <v>0.3442149456524636</v>
       </c>
       <c r="I12">
         <v>1075</v>
@@ -932,7 +932,7 @@
         <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -958,7 +958,7 @@
         <v>22</v>
       </c>
       <c r="H13">
-        <v>0.3990031874696494</v>
+        <v>0.3967632462557144</v>
       </c>
       <c r="I13">
         <v>148</v>
@@ -993,7 +993,7 @@
         <v>23</v>
       </c>
       <c r="H14">
-        <v>0.2735865854928065</v>
+        <v>0.2747062872847854</v>
       </c>
       <c r="I14">
         <v>371</v>
@@ -1063,7 +1063,7 @@
         <v>25</v>
       </c>
       <c r="H16">
-        <v>0.2252911974588692</v>
+        <v>0.2590555796461153</v>
       </c>
       <c r="I16">
         <v>6</v>
@@ -1098,7 +1098,7 @@
         <v>26</v>
       </c>
       <c r="H17">
-        <v>0.3792760390716836</v>
+        <v>0.377096797772938</v>
       </c>
       <c r="I17">
         <v>311</v>
@@ -1133,7 +1133,7 @@
         <v>27</v>
       </c>
       <c r="H18">
-        <v>0.3326118851802889</v>
+        <v>0.3340735231575941</v>
       </c>
       <c r="I18">
         <v>86</v>
@@ -1168,7 +1168,7 @@
         <v>28</v>
       </c>
       <c r="H19">
-        <v>0.3763389801133797</v>
+        <v>0.4295436971652442</v>
       </c>
       <c r="I19">
         <v>11</v>
@@ -1203,7 +1203,7 @@
         <v>29</v>
       </c>
       <c r="H20">
-        <v>0.3311969596911499</v>
+        <v>0.3313083410711778</v>
       </c>
       <c r="I20">
         <v>1538</v>
@@ -1273,7 +1273,7 @@
         <v>31</v>
       </c>
       <c r="H22">
-        <v>0.3600691554118552</v>
+        <v>0.360741111809918</v>
       </c>
       <c r="I22">
         <v>659</v>
@@ -1308,7 +1308,7 @@
         <v>32</v>
       </c>
       <c r="H23">
-        <v>0.3653669250472839</v>
+        <v>0.3617612931356188</v>
       </c>
       <c r="I23">
         <v>36</v>
@@ -1343,7 +1343,7 @@
         <v>33</v>
       </c>
       <c r="H24">
-        <v>0.3361505004067392</v>
+        <v>0.33791072420748</v>
       </c>
       <c r="I24">
         <v>154</v>
@@ -1378,7 +1378,7 @@
         <v>34</v>
       </c>
       <c r="H25">
-        <v>0.3227939733627909</v>
+        <v>0.3254112362531352</v>
       </c>
       <c r="I25">
         <v>275</v>
@@ -1413,7 +1413,7 @@
         <v>35</v>
       </c>
       <c r="H26">
-        <v>0.3186861343705282</v>
+        <v>0.3177654134214171</v>
       </c>
       <c r="I26">
         <v>367</v>
@@ -1448,7 +1448,7 @@
         <v>46</v>
       </c>
       <c r="H27">
-        <v>0.2587317072685264</v>
+        <v>0.2519680450765877</v>
       </c>
       <c r="I27">
         <v>79</v>
@@ -1483,7 +1483,7 @@
         <v>37</v>
       </c>
       <c r="H28">
-        <v>0.3323969193591774</v>
+        <v>0.333448198224901</v>
       </c>
       <c r="I28">
         <v>190</v>
@@ -1553,7 +1553,7 @@
         <v>39</v>
       </c>
       <c r="H30">
-        <v>0.2789931098576144</v>
+        <v>0.2798449904659316</v>
       </c>
       <c r="I30">
         <v>283</v>
@@ -1623,7 +1623,7 @@
         <v>41</v>
       </c>
       <c r="H32">
-        <v>0.3444100726783595</v>
+        <v>0.3365065710872929</v>
       </c>
       <c r="I32">
         <v>32</v>
@@ -1632,7 +1632,7 @@
         <v>45</v>
       </c>
       <c r="K32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1658,7 +1658,7 @@
         <v>42</v>
       </c>
       <c r="H33">
-        <v>0.2783312288900117</v>
+        <v>0.282238808387558</v>
       </c>
       <c r="I33">
         <v>62</v>
